--- a/2018/Mount2/Mount2_members_final.xlsx
+++ b/2018/Mount2/Mount2_members_final.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
